--- a/GourmetProject/GameConfig/Datas/__beans__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__beans__.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="4" min="2" max="2"/>
@@ -609,106 +609,257 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr"/>
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>RecipeEntry</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr"/>
+      <c r="D4" s="0" t="inlineStr"/>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>,</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>菜谱池随机条目：单元格写 dishId,weight,maxCount</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr">
         <is>
           <t>dishId</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="K4" s="0" t="inlineStr"/>
+      <c r="L4" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+      <c r="M4" s="0" t="inlineStr"/>
+      <c r="N4" s="0" t="inlineStr">
         <is>
           <t>菜品ID</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="O4" s="0" t="inlineStr"/>
+      <c r="P4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr"/>
+      <c r="B5" s="0" t="inlineStr"/>
+      <c r="C5" s="0" t="inlineStr"/>
+      <c r="D5" s="0" t="inlineStr"/>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="K5" s="0" t="inlineStr"/>
+      <c r="L5" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
+      <c r="M5" s="0" t="inlineStr"/>
+      <c r="N5" s="0" t="inlineStr">
         <is>
           <t>权重</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="O5" s="0" t="inlineStr"/>
+      <c r="P5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr"/>
+      <c r="B6" s="0" t="inlineStr"/>
+      <c r="C6" s="0" t="inlineStr"/>
+      <c r="D6" s="0" t="inlineStr"/>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr">
         <is>
           <t>maxCount</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="K6" s="0" t="inlineStr"/>
+      <c r="L6" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+      <c r="M6" s="0" t="inlineStr"/>
+      <c r="N6" s="0" t="inlineStr">
         <is>
           <t>最大数量(0=不限)</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="O6" s="0" t="inlineStr"/>
+      <c r="P6" s="0" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr"/>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>LevelWeightParams</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr"/>
+      <c r="D7" s="0" t="inlineStr"/>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>等级权重参数：单元格写 maxLevel,nextLevelWeightMultiplier,baseWeight</t>
+        </is>
+      </c>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>maxLevel</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr"/>
+      <c r="L7" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M7" s="0" t="inlineStr"/>
+      <c r="N7" s="0" t="inlineStr">
+        <is>
+          <t>最大等级(被动道具可升到的上限)</t>
+        </is>
+      </c>
+      <c r="O7" s="0" t="inlineStr"/>
+      <c r="P7" s="0" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr"/>
+      <c r="B8" s="0" t="inlineStr"/>
+      <c r="C8" s="0" t="inlineStr"/>
+      <c r="D8" s="0" t="inlineStr"/>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>nextLevelWeightMultiplier</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr"/>
+      <c r="L8" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M8" s="0" t="inlineStr"/>
+      <c r="N8" s="0" t="inlineStr">
+        <is>
+          <t>下一级权重倍率(已持有时再被抽中的权重系数)</t>
+        </is>
+      </c>
+      <c r="O8" s="0" t="inlineStr"/>
+      <c r="P8" s="0" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr"/>
+      <c r="B9" s="0" t="inlineStr"/>
+      <c r="C9" s="0" t="inlineStr"/>
+      <c r="D9" s="0" t="inlineStr"/>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>baseWeight</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr"/>
+      <c r="L9" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M9" s="0" t="inlineStr"/>
+      <c r="N9" s="0" t="inlineStr">
+        <is>
+          <t>随机基础权重</t>
+        </is>
+      </c>
+      <c r="O9" s="0" t="inlineStr"/>
+      <c r="P9" s="0" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HiddenRange</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>出现隐藏分区间：单元格写 min,max</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>出现隐藏分下限</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>出现隐藏分上限</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/GourmetProject/GameConfig/Datas/__beans__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__beans__.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="4" min="2" max="2"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>菜谱池随机条目：单元格写 dishId,weight,maxCount</t>
+          <t>菜谱池随机条目：单元格写 dishId,weight,maxCount,initScore</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr"/>
@@ -711,72 +711,59 @@
       <c r="P6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr"/>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>LevelWeightParams</t>
-        </is>
-      </c>
-      <c r="C7" s="0" t="inlineStr"/>
-      <c r="D7" s="0" t="inlineStr"/>
-      <c r="E7" s="0" t="inlineStr"/>
-      <c r="F7" s="0" t="inlineStr">
-        <is>
-          <t>,</t>
-        </is>
-      </c>
-      <c r="G7" s="0" t="inlineStr">
-        <is>
-          <t>等级权重参数：单元格写 maxLevel,nextLevelWeightMultiplier,baseWeight</t>
-        </is>
-      </c>
-      <c r="H7" s="0" t="inlineStr"/>
-      <c r="I7" s="0" t="inlineStr"/>
-      <c r="J7" s="0" t="inlineStr">
-        <is>
-          <t>maxLevel</t>
-        </is>
-      </c>
-      <c r="K7" s="0" t="inlineStr"/>
-      <c r="L7" s="0" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>initScore</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="M7" s="0" t="inlineStr"/>
-      <c r="N7" s="0" t="inlineStr">
-        <is>
-          <t>最大等级(被动道具可升到的上限)</t>
-        </is>
-      </c>
-      <c r="O7" s="0" t="inlineStr"/>
-      <c r="P7" s="0" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>本菜谱内初始分（用于累计 requiredInitScore）</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr"/>
-      <c r="B8" s="0" t="inlineStr"/>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>LevelWeightParams</t>
+        </is>
+      </c>
       <c r="C8" s="0" t="inlineStr"/>
       <c r="D8" s="0" t="inlineStr"/>
       <c r="E8" s="0" t="inlineStr"/>
-      <c r="F8" s="0" t="inlineStr"/>
-      <c r="G8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>等级权重参数：单元格写 maxLevel,nextLevelWeightMultiplier,baseWeight</t>
+        </is>
+      </c>
       <c r="H8" s="0" t="inlineStr"/>
       <c r="I8" s="0" t="inlineStr"/>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t>nextLevelWeightMultiplier</t>
+          <t>maxLevel</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr"/>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="M8" s="0" t="inlineStr"/>
       <c r="N8" s="0" t="inlineStr">
         <is>
-          <t>下一级权重倍率(已持有时再被抽中的权重系数)</t>
+          <t>最大等级(被动道具可升到的上限)</t>
         </is>
       </c>
       <c r="O8" s="0" t="inlineStr"/>
@@ -794,7 +781,7 @@
       <c r="I9" s="0" t="inlineStr"/>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t>baseWeight</t>
+          <t>nextLevelWeightMultiplier</t>
         </is>
       </c>
       <c r="K9" s="0" t="inlineStr"/>
@@ -806,56 +793,86 @@
       <c r="M9" s="0" t="inlineStr"/>
       <c r="N9" s="0" t="inlineStr">
         <is>
-          <t>随机基础权重</t>
+          <t>下一级权重倍率(已持有时再被抽中的权重系数)</t>
         </is>
       </c>
       <c r="O9" s="0" t="inlineStr"/>
       <c r="P9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr"/>
+      <c r="B10" s="0" t="inlineStr"/>
+      <c r="C10" s="0" t="inlineStr"/>
+      <c r="D10" s="0" t="inlineStr"/>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>baseWeight</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr"/>
+      <c r="L10" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M10" s="0" t="inlineStr"/>
+      <c r="N10" s="0" t="inlineStr">
+        <is>
+          <t>随机基础权重</t>
+        </is>
+      </c>
+      <c r="O10" s="0" t="inlineStr"/>
+      <c r="P10" s="0" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>HiddenRange</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" s="0" t="inlineStr">
         <is>
           <t>,</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>出现隐藏分区间：单元格写 min,max</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J11" s="0" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L11" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N11" s="0" t="inlineStr">
         <is>
           <t>出现隐藏分下限</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="J11" t="inlineStr">
+    <row r="12">
+      <c r="J12" s="0" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L12" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N12" s="0" t="inlineStr">
         <is>
           <t>出现隐藏分上限</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/__beans__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__beans__.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="4" min="2" max="2"/>
@@ -711,32 +711,28 @@
       <c r="P6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="0" t="inlineStr">
         <is>
           <t>initScore</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="0" t="inlineStr">
         <is>
           <t>本菜谱内初始分（用于累计 requiredInitScore）</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr"/>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>LevelWeightParams</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="inlineStr"/>
-      <c r="D8" s="0" t="inlineStr"/>
-      <c r="E8" s="0" t="inlineStr"/>
+          <t>HiddenRange</t>
+        </is>
+      </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
           <t>,</t>
@@ -744,135 +740,37 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>等级权重参数：单元格写 maxLevel,nextLevelWeightMultiplier,baseWeight</t>
-        </is>
-      </c>
-      <c r="H8" s="0" t="inlineStr"/>
-      <c r="I8" s="0" t="inlineStr"/>
+          <t>出现隐藏分区间：单元格写 min,max</t>
+        </is>
+      </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t>maxLevel</t>
-        </is>
-      </c>
-      <c r="K8" s="0" t="inlineStr"/>
+          <t>min</t>
+        </is>
+      </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="M8" s="0" t="inlineStr"/>
       <c r="N8" s="0" t="inlineStr">
         <is>
-          <t>最大等级(被动道具可升到的上限)</t>
-        </is>
-      </c>
-      <c r="O8" s="0" t="inlineStr"/>
-      <c r="P8" s="0" t="inlineStr"/>
+          <t>出现隐藏分下限</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr"/>
-      <c r="B9" s="0" t="inlineStr"/>
-      <c r="C9" s="0" t="inlineStr"/>
-      <c r="D9" s="0" t="inlineStr"/>
-      <c r="E9" s="0" t="inlineStr"/>
-      <c r="F9" s="0" t="inlineStr"/>
-      <c r="G9" s="0" t="inlineStr"/>
-      <c r="H9" s="0" t="inlineStr"/>
-      <c r="I9" s="0" t="inlineStr"/>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t>nextLevelWeightMultiplier</t>
-        </is>
-      </c>
-      <c r="K9" s="0" t="inlineStr"/>
+          <t>max</t>
+        </is>
+      </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="M9" s="0" t="inlineStr"/>
+          <t>int</t>
+        </is>
+      </c>
       <c r="N9" s="0" t="inlineStr">
-        <is>
-          <t>下一级权重倍率(已持有时再被抽中的权重系数)</t>
-        </is>
-      </c>
-      <c r="O9" s="0" t="inlineStr"/>
-      <c r="P9" s="0" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="inlineStr"/>
-      <c r="B10" s="0" t="inlineStr"/>
-      <c r="C10" s="0" t="inlineStr"/>
-      <c r="D10" s="0" t="inlineStr"/>
-      <c r="E10" s="0" t="inlineStr"/>
-      <c r="F10" s="0" t="inlineStr"/>
-      <c r="G10" s="0" t="inlineStr"/>
-      <c r="H10" s="0" t="inlineStr"/>
-      <c r="I10" s="0" t="inlineStr"/>
-      <c r="J10" s="0" t="inlineStr">
-        <is>
-          <t>baseWeight</t>
-        </is>
-      </c>
-      <c r="K10" s="0" t="inlineStr"/>
-      <c r="L10" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="M10" s="0" t="inlineStr"/>
-      <c r="N10" s="0" t="inlineStr">
-        <is>
-          <t>随机基础权重</t>
-        </is>
-      </c>
-      <c r="O10" s="0" t="inlineStr"/>
-      <c r="P10" s="0" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t>HiddenRange</t>
-        </is>
-      </c>
-      <c r="F11" s="0" t="inlineStr">
-        <is>
-          <t>,</t>
-        </is>
-      </c>
-      <c r="G11" s="0" t="inlineStr">
-        <is>
-          <t>出现隐藏分区间：单元格写 min,max</t>
-        </is>
-      </c>
-      <c r="J11" s="0" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="L11" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N11" s="0" t="inlineStr">
-        <is>
-          <t>出现隐藏分下限</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="J12" s="0" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
-      </c>
-      <c r="L12" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N12" s="0" t="inlineStr">
         <is>
           <t>出现隐藏分上限</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/__beans__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__beans__.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="4" min="2" max="2"/>
@@ -776,6 +776,55 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>ActionSmallGroupEntry</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>行动中组的小组候选条目：单元格写 smallGroupId,weight</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>smallGroupId</t>
+        </is>
+      </c>
+      <c r="L10" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N10" s="0" t="inlineStr">
+        <is>
+          <t>小组ID→small_group.id</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="L11" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N11" s="0" t="inlineStr">
+        <is>
+          <t>中组内选该小组的权重</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>

--- a/GourmetProject/GameConfig/Datas/__beans__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__beans__.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="4" min="2" max="2"/>
@@ -776,55 +776,6 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t>ActionSmallGroupEntry</t>
-        </is>
-      </c>
-      <c r="F10" s="0" t="inlineStr">
-        <is>
-          <t>,</t>
-        </is>
-      </c>
-      <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t>行动中组的小组候选条目：单元格写 smallGroupId,weight</t>
-        </is>
-      </c>
-      <c r="J10" s="0" t="inlineStr">
-        <is>
-          <t>smallGroupId</t>
-        </is>
-      </c>
-      <c r="L10" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N10" s="0" t="inlineStr">
-        <is>
-          <t>小组ID→small_group.id</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="J11" s="0" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-      <c r="L11" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N11" s="0" t="inlineStr">
-        <is>
-          <t>中组内选该小组的权重</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>

--- a/GourmetProject/GameConfig/Datas/__beans__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__beans__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbf5013c8820d4fb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re7929d3999704b25"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -546,7 +546,7 @@
         </x:is>
       </x:c>
       <x:c r="G4" t="str">
-        <x:v>菜谱小组随机条目：单元格写 dishId,weight,maxCount</x:v>
+        <x:v>食谱小组随机条目：单元格写 dishId,weight,maxCount</x:v>
       </x:c>
       <x:c r="H4" t="inlineStr">
         <x:is>
@@ -578,10 +578,8 @@
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="N4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">菜品ID</x:t>
-        </x:is>
+      <x:c r="N4" t="str">
+        <x:v>食物ID</x:v>
       </x:c>
       <x:c r="O4" t="inlineStr">
         <x:is>
@@ -823,7 +821,7 @@
         <x:v>;</x:v>
       </x:c>
       <x:c r="G10" t="str">
-        <x:v>菜谱带权数量方案：单元格写 count1,count2,...;weight</x:v>
+        <x:v>食谱带权数量方案：单元格写 count1,count2,...;weight</x:v>
       </x:c>
       <x:c r="H10"/>
       <x:c r="I10"/>
